--- a/clients/大晃産業/04_参加者管理/【メンバー構成表】管理職候補育成プログラム.xlsx
+++ b/clients/大晃産業/04_参加者管理/【メンバー構成表】管理職候補育成プログラム.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -84,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +101,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -139,6 +170,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,11 +581,11 @@
           <t>■ 塾長（1名）― 研修全体の最高責任者。経営層・役員クラスの方。参加可能な回にオブザーブとして出席。</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -596,49 +636,53 @@
           <t>■ コーディネーター（4名）― 各チームのリーダー役。部長クラスの方。塾生3名を担当し、研修での学びを職場実践につなげるサポートを行う。</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>役職</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>所属部署</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>担当チーム（A/B/C/D）</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>特徴・スキル・備考</t>
         </is>
       </c>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="n">
@@ -650,6 +694,8 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -661,6 +707,8 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -672,6 +720,8 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -683,6 +733,8 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
     </row>
     <row r="14" ht="10" customHeight="1"/>
     <row r="15" ht="30" customHeight="1">
@@ -691,14 +743,14 @@
           <t>■ 塾生（12名）― 研修の受講生。課長・次長クラス（将来の部長候補）。全12回に参加。</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -955,19 +1007,24 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="17">
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G9:I9"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G12:I12"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A30:I30"/>
+    <mergeCell ref="G11:I11"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
